--- a/fixtures/golden/simple-excel/canonical.xlsx
+++ b/fixtures/golden/simple-excel/canonical.xlsx
@@ -583,7 +583,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,7 +2473,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2616,7 +2614,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2636,7 +2633,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
